--- a/docs/Lab01/Lab01_ReviewReport.xlsx
+++ b/docs/Lab01/Lab01_ReviewReport.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Laptop\e\VVSS\CamiVVSS_ro2025-2026\Labs\CheckListsAll\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ungur\OneDrive\Desktop\AN_3\SEM2\vvss\Lab01\CheckLists\CheckLists\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFE83867-3721-469D-B0A3-67FDA22FF09F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0641048-5E8C-492D-B2DC-51608FCDC6C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="650" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="650" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Requirements Phase Defects" sheetId="7" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="81">
   <si>
     <t>Document  Title:</t>
   </si>
@@ -71,15 +71,6 @@
     <t xml:space="preserve">Author Name: </t>
   </si>
   <si>
-    <t>Popescu Ionel</t>
-  </si>
-  <si>
-    <t>Georgescu Anca</t>
-  </si>
-  <si>
-    <t>Firicescu George</t>
-  </si>
-  <si>
     <t>Requirements Document</t>
   </si>
   <si>
@@ -135,13 +126,751 @@
   </si>
   <si>
     <t>Effort to perform tool-based code analysis (hours):</t>
+  </si>
+  <si>
+    <t>Ungurean Catalina, Vranciu Andra, Zaharia Ilinca</t>
+  </si>
+  <si>
+    <t>Zaharia Ilinca</t>
+  </si>
+  <si>
+    <t>Vranciu Andra</t>
+  </si>
+  <si>
+    <t>Ungurean Catalina</t>
+  </si>
+  <si>
+    <t>R01</t>
+  </si>
+  <si>
+    <t>R02</t>
+  </si>
+  <si>
+    <t>R04</t>
+  </si>
+  <si>
+    <t>Pag1</t>
+  </si>
+  <si>
+    <t>0.25</t>
+  </si>
+  <si>
+    <t>Linia 45 - StocService</t>
+  </si>
+  <si>
+    <t>C06</t>
+  </si>
+  <si>
+    <t>C08</t>
+  </si>
+  <si>
+    <t>C01</t>
+  </si>
+  <si>
+    <t>Linia 25,36- FileAbstractRepository</t>
+  </si>
+  <si>
+    <t>Linia 16 - CsvEExporter</t>
+  </si>
+  <si>
+    <t>A5</t>
+  </si>
+  <si>
+    <t>A9</t>
+  </si>
+  <si>
+    <t>A10</t>
+  </si>
+  <si>
+    <t>Enum</t>
+  </si>
+  <si>
+    <t>Clasa Stoc</t>
+  </si>
+  <si>
+    <t>Exceptii</t>
+  </si>
+  <si>
+    <t>Clasa Stoc este izolată și are doar un câmp de tip String pentru ingredient. Nu există o asociere clară în diagramă între Stoc și o entitate Ingredient. Imbunatatire: Crearea unei clase Ingredient și adăugarea unei relații de asociere (1 la 1) între Stoc și Ingredient.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">La scăderea cantității din stoc la plasarea unei comenzi, se face un cast explicit la </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>(int)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> deși cantitatea este </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>double</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>s.setCantitate((int)(s.getCantitate() - deScazut));</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>). Asta duce la pierderea zecimalelor (ex: dacă se consumă 0.5 litri de lapte).Imbunatatire</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> eliminarea cast-ului la int. Cod corect: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>s.setCantitate(s.getCantitate() - deScazut);</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">În metodele </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>loadFromFile()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> și </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>writeToFile()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, excepțiile de tip </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>IOException</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> sunt doar printate în consolă (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>e.printStackTrace();</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>) și ascunse. Dacă fișierul nu poate fi scris/citit, programul continuă să ruleze corupt fără să avertizeze utilizatorul.Imbunatatire</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> aruncarea unei excepții pentru a opri execuția sau a notifica UI-ul: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>throw new RuntimeException(e);</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Căutarea produsului dintr-o comandă pentru a-l exporta se face folosind </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>.toList().get(0)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Dacă produsul a fost între timp șters din sistem, lista va fi goală și </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>.get(0)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> va arunca </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>IndexOutOfBoundsException</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, crăpând aplicația. Imbunatatire</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> folosirea </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>.findFirst().orElse(null)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> și verificarea dacă produsul este null înainte de a scrie în CSV.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>În arhitectură este definită o singură excepție custom (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>ValidationException</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>). Nu există o strategie clară pentru erorile de persistență (ex: fișier lipsă, id duplicat). Imbunatatire</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Adăugarea unei clase </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>RepositoryException</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> pentru a separa erorile de validare de cele de persistență a datelor.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">TipBautura și </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>CategorieBautura</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> sunt modelate ca </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Enum</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. Conform cerințelor, utilizatorul trebuie să poată adăuga/șterge categorii la runtime, ceea ce este imposibil cu Enums. Imbnatatire</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Transformarea lor din </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Enum</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> în </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Clase</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (Entități) și crearea de Repository-uri pentru ele.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Nu se specifică ce se întâmplă dacă un produs comandat necesită mai multe ingrediente decât există momentan în stoc. Imbunatatire </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> aplicația va afișa eroare și va bloca comanda dacă stocul e insuficient</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Nu se specifică starea sistemului dacă fișierele text nu există. Imbunatatire</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> la prima rulare, dacă fișierele lipsesc, aplicația le va crea automat goale</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Se cere administrarea ingredientelor, dar lipsesc operațiile de bază.. Imbunatatire</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ut</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ilizatorul poate adăuga, modifica și șterge ingrediente</t>
+    </r>
+  </si>
+  <si>
+    <t>0.75</t>
+  </si>
+  <si>
+    <t>Add a private constructor to hide the implicit public one.</t>
+  </si>
+  <si>
+    <t>Remove the parentheses around the "p1" parameter</t>
+  </si>
+  <si>
+    <t>Use multiple calls to "append" instead of string concatenation.</t>
+  </si>
+  <si>
+    <t>private ReceiptGenerator() {}</t>
+  </si>
+  <si>
+    <t>Nu are constructor definit</t>
+  </si>
+  <si>
+    <t>(p1)-&gt;i.getProduct().getId()==p1.getId()</t>
+  </si>
+  <si>
+    <t>p1 -&gt; i.getProduct().getId()==p1.getId()</t>
+  </si>
+  <si>
+    <t>sb.append(p.getNume()+": ")</t>
+  </si>
+  <si>
+    <t>sb.append(p.getNume()).append(": ")</t>
+  </si>
+  <si>
+    <t>Make non-static "product" transient or serializable.</t>
+  </si>
+  <si>
+    <t>public class Product {</t>
+  </si>
+  <si>
+    <t>Use a StringBuilder instead.</t>
+  </si>
+  <si>
+    <t>String errors = ""; (și concatenările cu +=)</t>
+  </si>
+  <si>
+    <t>ReceiptGenerator linia 11</t>
+  </si>
+  <si>
+    <t>ReceiptGenerator linia 17</t>
+  </si>
+  <si>
+    <t>ReceiptGenerator linia 18</t>
+  </si>
+  <si>
+    <t>OrderValidator linia 25</t>
+  </si>
+  <si>
+    <t>OrderItem linia 7</t>
+  </si>
+  <si>
+    <t>private transient Product product;</t>
+  </si>
+  <si>
+    <r>
+      <t>StringBuilder errors = new StringBuilder();</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (și </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>errors.append(...)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -224,6 +953,36 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -326,7 +1085,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -398,6 +1157,23 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -707,95 +1483,111 @@
     <tabColor theme="7" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="A1:J27"/>
-  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.9296875" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="8.90625" style="6"/>
-    <col min="2" max="2" width="12.26953125" style="6" customWidth="1"/>
-    <col min="3" max="4" width="16.26953125" style="6" customWidth="1"/>
-    <col min="5" max="5" width="41.453125" style="6" customWidth="1"/>
-    <col min="6" max="8" width="8.90625" style="6"/>
+    <col min="1" max="1" width="8.9296875" style="6"/>
+    <col min="2" max="2" width="12.265625" style="6" customWidth="1"/>
+    <col min="3" max="4" width="16.265625" style="6" customWidth="1"/>
+    <col min="5" max="5" width="67.59765625" style="6" customWidth="1"/>
+    <col min="6" max="8" width="8.9296875" style="6"/>
     <col min="9" max="9" width="21" style="6" customWidth="1"/>
-    <col min="10" max="10" width="14.453125" style="6" customWidth="1"/>
-    <col min="11" max="16384" width="8.90625" style="6"/>
+    <col min="10" max="10" width="14.46484375" style="6" customWidth="1"/>
+    <col min="11" max="16384" width="8.9296875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" ht="15.75">
       <c r="A1" s="4"/>
       <c r="B1" s="5" t="s">
         <v>3</v>
       </c>
       <c r="H1" s="23" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="I1" s="23"/>
       <c r="J1" s="23"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10">
       <c r="B2" s="24" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C2" s="24"/>
       <c r="D2" s="24"/>
       <c r="E2" s="24"/>
       <c r="H2" s="3"/>
       <c r="I2" s="19" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J2" s="17" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="H3" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="I3" s="17"/>
-      <c r="J3" s="17"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+        <v>17</v>
+      </c>
+      <c r="I3" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="J3" s="17">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="C4" s="13" t="s">
         <v>0</v>
       </c>
       <c r="D4" s="25" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E4" s="25"/>
       <c r="H4" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J4" s="3">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
       <c r="C5" s="13" t="s">
         <v>9</v>
       </c>
       <c r="D5" s="26" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="E5" s="27"/>
       <c r="H5" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+        <v>19</v>
+      </c>
+      <c r="I5" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="J5" s="3">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
       <c r="B6" s="8"/>
       <c r="C6" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="22"/>
+      <c r="D6" s="22" t="s">
+        <v>30</v>
+      </c>
       <c r="E6" s="22"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10">
       <c r="C7" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="22"/>
+      <c r="D7" s="37">
+        <v>46094</v>
+      </c>
       <c r="E7" s="22"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10">
       <c r="B9" s="10" t="s">
         <v>4</v>
       </c>
@@ -809,33 +1601,51 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B10" s="3">
+    <row r="10" spans="1:10" ht="42.75">
+      <c r="B10" s="38">
         <v>1</v>
       </c>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="2"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B11" s="3">
+      <c r="C10" s="39" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" s="40" t="s">
+        <v>37</v>
+      </c>
+      <c r="E10" s="39" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="28.5">
+      <c r="B11" s="38">
         <f>B10+1</f>
         <v>2</v>
       </c>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="2"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B12" s="3">
+      <c r="C11" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="D11" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="E11" s="39" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="28.5">
+      <c r="B12" s="38">
         <f t="shared" ref="B12:B25" si="0">B11+1</f>
         <v>3</v>
       </c>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="2"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="C12" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="D12" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="E12" s="39" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
       <c r="B13" s="3">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -844,7 +1654,7 @@
       <c r="D13" s="1"/>
       <c r="E13" s="2"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:10">
       <c r="B14" s="3">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -853,7 +1663,7 @@
       <c r="D14" s="1"/>
       <c r="E14" s="2"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:10">
       <c r="B15" s="3">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -862,7 +1672,7 @@
       <c r="D15" s="1"/>
       <c r="E15" s="2"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:10">
       <c r="B16" s="3">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -871,7 +1681,7 @@
       <c r="D16" s="1"/>
       <c r="E16" s="2"/>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:5">
       <c r="B17" s="3">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -880,7 +1690,7 @@
       <c r="D17" s="1"/>
       <c r="E17" s="2"/>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:5">
       <c r="B18" s="3">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -889,7 +1699,7 @@
       <c r="D18" s="3"/>
       <c r="E18" s="15"/>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:5">
       <c r="B19" s="3">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -898,7 +1708,7 @@
       <c r="D19" s="3"/>
       <c r="E19" s="15"/>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:5">
       <c r="B20" s="3">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -907,7 +1717,7 @@
       <c r="D20" s="3"/>
       <c r="E20" s="15"/>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:5">
       <c r="B21" s="3">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -916,7 +1726,7 @@
       <c r="D21" s="3"/>
       <c r="E21" s="15"/>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:5">
       <c r="B22" s="3">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -925,7 +1735,7 @@
       <c r="D22" s="3"/>
       <c r="E22" s="15"/>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:5">
       <c r="B23" s="3">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -934,7 +1744,7 @@
       <c r="D23" s="3"/>
       <c r="E23" s="15"/>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:5">
       <c r="B24" s="3">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -943,7 +1753,7 @@
       <c r="D24" s="3"/>
       <c r="E24" s="15"/>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:5">
       <c r="B25" s="3">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -952,12 +1762,14 @@
       <c r="D25" s="3"/>
       <c r="E25" s="15"/>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:5">
       <c r="C27" s="11" t="s">
         <v>8</v>
       </c>
       <c r="D27" s="12"/>
-      <c r="E27" s="1"/>
+      <c r="E27" s="1" t="s">
+        <v>38</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -979,94 +1791,110 @@
     <tabColor theme="9" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="A1:J28"/>
-  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.9296875" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="8.90625" style="6"/>
-    <col min="2" max="2" width="12.26953125" style="6" customWidth="1"/>
-    <col min="3" max="4" width="16.26953125" style="6" customWidth="1"/>
-    <col min="5" max="5" width="41.453125" style="6" customWidth="1"/>
-    <col min="6" max="8" width="8.90625" style="6"/>
-    <col min="9" max="9" width="22.08984375" style="6" customWidth="1"/>
-    <col min="10" max="16384" width="8.90625" style="6"/>
+    <col min="1" max="1" width="8.9296875" style="6"/>
+    <col min="2" max="2" width="12.265625" style="6" customWidth="1"/>
+    <col min="3" max="4" width="16.265625" style="6" customWidth="1"/>
+    <col min="5" max="5" width="41.46484375" style="6" customWidth="1"/>
+    <col min="6" max="8" width="8.9296875" style="6"/>
+    <col min="9" max="9" width="22.06640625" style="6" customWidth="1"/>
+    <col min="10" max="16384" width="8.9296875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" ht="15.75">
       <c r="A1" s="4"/>
       <c r="B1" s="5" t="s">
         <v>3</v>
       </c>
       <c r="H1" s="23" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="I1" s="23"/>
       <c r="J1" s="23"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10">
       <c r="B2" s="24" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C2" s="24"/>
       <c r="D2" s="24"/>
       <c r="E2" s="24"/>
       <c r="H2" s="3"/>
       <c r="I2" s="19" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J2" s="17" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="H3" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="I3" s="17"/>
-      <c r="J3" s="17"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+        <v>17</v>
+      </c>
+      <c r="I3" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="J3" s="17">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="C4" s="7" t="s">
         <v>0</v>
       </c>
       <c r="D4" s="28" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E4" s="28"/>
       <c r="H4" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J4" s="3">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
       <c r="C5" s="7" t="s">
         <v>10</v>
       </c>
       <c r="D5" s="29" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="E5" s="30"/>
       <c r="H5" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+        <v>19</v>
+      </c>
+      <c r="I5" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="J5" s="3">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
       <c r="B6" s="8"/>
       <c r="C6" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="22"/>
+      <c r="D6" s="22" t="s">
+        <v>30</v>
+      </c>
       <c r="E6" s="22"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10">
       <c r="C7" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="22"/>
+      <c r="D7" s="37">
+        <v>46094</v>
+      </c>
       <c r="E7" s="22"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10">
       <c r="B9" s="10" t="s">
         <v>4</v>
       </c>
@@ -1080,33 +1908,51 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B10" s="3">
+    <row r="10" spans="1:10" ht="85.5">
+      <c r="B10" s="38">
         <v>1</v>
       </c>
-      <c r="C10" s="1"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B11" s="3">
+      <c r="C10" s="38" t="s">
+        <v>45</v>
+      </c>
+      <c r="D10" s="39" t="s">
+        <v>50</v>
+      </c>
+      <c r="E10" s="39" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="85.5">
+      <c r="B11" s="38">
         <f>B10+1</f>
         <v>2</v>
       </c>
-      <c r="C11" s="1"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B12" s="3">
+      <c r="C11" s="38" t="s">
+        <v>46</v>
+      </c>
+      <c r="D11" s="39" t="s">
+        <v>49</v>
+      </c>
+      <c r="E11" s="39" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="85.5">
+      <c r="B12" s="38">
         <f t="shared" ref="B12:B26" si="0">B11+1</f>
         <v>3</v>
       </c>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="2"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="C12" s="38" t="s">
+        <v>47</v>
+      </c>
+      <c r="D12" s="38" t="s">
+        <v>48</v>
+      </c>
+      <c r="E12" s="39" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
       <c r="B13" s="3">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -1115,7 +1961,7 @@
       <c r="D13" s="1"/>
       <c r="E13" s="2"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:10">
       <c r="B14" s="3">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -1124,7 +1970,7 @@
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:10">
       <c r="B15" s="3">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -1133,7 +1979,7 @@
       <c r="D15" s="1"/>
       <c r="E15" s="2"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:10">
       <c r="B16" s="3">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -1142,7 +1988,7 @@
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:5">
       <c r="B17" s="3">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -1151,7 +1997,7 @@
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:5">
       <c r="B18" s="3">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -1160,7 +2006,7 @@
       <c r="D18" s="1"/>
       <c r="E18" s="2"/>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:5">
       <c r="B19" s="3">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -1169,7 +2015,7 @@
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:5">
       <c r="B20" s="3">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -1178,7 +2024,7 @@
       <c r="D20" s="1"/>
       <c r="E20" s="2"/>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:5">
       <c r="B21" s="3">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -1187,7 +2033,7 @@
       <c r="D21" s="1"/>
       <c r="E21" s="2"/>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:5">
       <c r="B22" s="3">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -1196,7 +2042,7 @@
       <c r="D22" s="1"/>
       <c r="E22" s="2"/>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:5">
       <c r="B23" s="3">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -1205,7 +2051,7 @@
       <c r="D23" s="1"/>
       <c r="E23" s="2"/>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:5">
       <c r="B24" s="3">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -1214,7 +2060,7 @@
       <c r="D24" s="1"/>
       <c r="E24" s="2"/>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:5">
       <c r="B25" s="3">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -1223,7 +2069,7 @@
       <c r="D25" s="1"/>
       <c r="E25" s="2"/>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:5">
       <c r="B26" s="3">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -1232,12 +2078,14 @@
       <c r="D26" s="1"/>
       <c r="E26" s="2"/>
     </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:5">
       <c r="C28" s="11" t="s">
         <v>8</v>
       </c>
       <c r="D28" s="12"/>
-      <c r="E28" s="1"/>
+      <c r="E28" s="1" t="s">
+        <v>38</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -1259,95 +2107,111 @@
     <tabColor theme="3" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="A1:J32"/>
-  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.9296875" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="8.90625" style="6"/>
-    <col min="2" max="2" width="12.26953125" style="6" customWidth="1"/>
-    <col min="3" max="3" width="16.26953125" style="6" customWidth="1"/>
+    <col min="1" max="1" width="8.9296875" style="6"/>
+    <col min="2" max="2" width="12.265625" style="6" customWidth="1"/>
+    <col min="3" max="3" width="16.265625" style="6" customWidth="1"/>
     <col min="4" max="4" width="18" style="6" customWidth="1"/>
-    <col min="5" max="5" width="41.453125" style="6" customWidth="1"/>
-    <col min="6" max="8" width="8.90625" style="6"/>
-    <col min="9" max="9" width="26.7265625" style="6" customWidth="1"/>
-    <col min="10" max="16384" width="8.90625" style="6"/>
+    <col min="5" max="5" width="41.46484375" style="6" customWidth="1"/>
+    <col min="6" max="8" width="8.9296875" style="6"/>
+    <col min="9" max="9" width="26.73046875" style="6" customWidth="1"/>
+    <col min="10" max="16384" width="8.9296875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" ht="15.75">
       <c r="A1" s="4"/>
       <c r="B1" s="5" t="s">
         <v>3</v>
       </c>
       <c r="H1" s="23" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="I1" s="23"/>
       <c r="J1" s="23"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10">
       <c r="B2" s="24" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C2" s="24"/>
       <c r="D2" s="24"/>
       <c r="E2" s="24"/>
       <c r="H2" s="3"/>
       <c r="I2" s="19" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J2" s="17" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="H3" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="I3" s="17"/>
-      <c r="J3" s="17"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+        <v>17</v>
+      </c>
+      <c r="I3" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="J3" s="17">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="C4" s="16" t="s">
         <v>0</v>
       </c>
       <c r="D4" s="31" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E4" s="31"/>
       <c r="H4" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J4" s="3">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
       <c r="C5" s="16" t="s">
         <v>9</v>
       </c>
       <c r="D5" s="32" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="E5" s="33"/>
       <c r="H5" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+        <v>19</v>
+      </c>
+      <c r="I5" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="J5" s="3">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
       <c r="B6" s="8"/>
       <c r="C6" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="22"/>
+      <c r="D6" s="22" t="s">
+        <v>30</v>
+      </c>
       <c r="E6" s="22"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10">
       <c r="C7" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="22"/>
+      <c r="D7" s="37">
+        <v>46094</v>
+      </c>
       <c r="E7" s="22"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10">
       <c r="B9" s="10" t="s">
         <v>4</v>
       </c>
@@ -1361,33 +2225,51 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B10" s="3">
+    <row r="10" spans="1:10" ht="126.75">
+      <c r="B10" s="38">
         <v>1</v>
       </c>
-      <c r="C10" s="1"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B11" s="3">
+      <c r="C10" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="D10" s="39" t="s">
+        <v>39</v>
+      </c>
+      <c r="E10" s="39" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="112.5">
+      <c r="B11" s="38">
         <f>B10+1</f>
         <v>2</v>
       </c>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="2"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B12" s="3">
+      <c r="C11" s="38" t="s">
+        <v>41</v>
+      </c>
+      <c r="D11" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="E11" s="39" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="114">
+      <c r="B12" s="38">
         <f t="shared" ref="B12:B30" si="0">B11+1</f>
         <v>3</v>
       </c>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="2"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="C12" s="38" t="s">
+        <v>42</v>
+      </c>
+      <c r="D12" s="38" t="s">
+        <v>44</v>
+      </c>
+      <c r="E12" s="39" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
       <c r="B13" s="3">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -1396,7 +2278,7 @@
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:10">
       <c r="B14" s="3">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -1405,7 +2287,7 @@
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:10">
       <c r="B15" s="3">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -1414,7 +2296,7 @@
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:10">
       <c r="B16" s="3">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -1423,7 +2305,7 @@
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:5">
       <c r="B17" s="3">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -1432,7 +2314,7 @@
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:5">
       <c r="B18" s="3">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -1441,7 +2323,7 @@
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:5">
       <c r="B19" s="3">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -1450,7 +2332,7 @@
       <c r="D19" s="1"/>
       <c r="E19" s="2"/>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:5">
       <c r="B20" s="3">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -1459,7 +2341,7 @@
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:5">
       <c r="B21" s="3">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -1468,7 +2350,7 @@
       <c r="D21" s="1"/>
       <c r="E21" s="2"/>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:5">
       <c r="B22" s="3">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -1477,7 +2359,7 @@
       <c r="D22" s="2"/>
       <c r="E22" s="2"/>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:5">
       <c r="B23" s="3">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -1486,7 +2368,7 @@
       <c r="D23" s="2"/>
       <c r="E23" s="2"/>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:5">
       <c r="B24" s="3">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -1495,7 +2377,7 @@
       <c r="D24" s="2"/>
       <c r="E24" s="2"/>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:5">
       <c r="B25" s="3">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -1504,7 +2386,7 @@
       <c r="D25" s="2"/>
       <c r="E25" s="2"/>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:5">
       <c r="B26" s="3">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -1513,7 +2395,7 @@
       <c r="D26" s="1"/>
       <c r="E26" s="2"/>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:5">
       <c r="B27" s="3">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -1522,7 +2404,7 @@
       <c r="D27" s="2"/>
       <c r="E27" s="1"/>
     </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:5">
       <c r="B28" s="3">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -1531,7 +2413,7 @@
       <c r="D28" s="2"/>
       <c r="E28" s="2"/>
     </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:5">
       <c r="B29" s="3">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -1540,7 +2422,7 @@
       <c r="D29" s="2"/>
       <c r="E29" s="2"/>
     </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:5">
       <c r="B30" s="3">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -1549,12 +2431,14 @@
       <c r="D30" s="2"/>
       <c r="E30" s="2"/>
     </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:5">
       <c r="C32" s="11" t="s">
         <v>8</v>
       </c>
       <c r="D32" s="12"/>
-      <c r="E32" s="1"/>
+      <c r="E32" s="1" t="s">
+        <v>38</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -1576,152 +2460,208 @@
     <tabColor theme="6" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:J35"/>
-  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.9296875" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="8.90625" style="6"/>
-    <col min="2" max="2" width="12.26953125" style="6" customWidth="1"/>
-    <col min="3" max="3" width="16.26953125" style="6" customWidth="1"/>
+    <col min="1" max="1" width="8.9296875" style="6"/>
+    <col min="2" max="2" width="12.265625" style="6" customWidth="1"/>
+    <col min="3" max="3" width="16.265625" style="6" customWidth="1"/>
     <col min="4" max="4" width="18" style="6" customWidth="1"/>
-    <col min="5" max="5" width="23.90625" style="6" customWidth="1"/>
-    <col min="6" max="6" width="16.6328125" style="6" customWidth="1"/>
-    <col min="7" max="8" width="8.90625" style="6"/>
-    <col min="9" max="9" width="26.7265625" style="6" customWidth="1"/>
-    <col min="10" max="16384" width="8.90625" style="6"/>
+    <col min="5" max="5" width="23.9296875" style="6" customWidth="1"/>
+    <col min="6" max="6" width="16.59765625" style="6" customWidth="1"/>
+    <col min="7" max="8" width="8.9296875" style="6"/>
+    <col min="9" max="9" width="26.73046875" style="6" customWidth="1"/>
+    <col min="10" max="16384" width="8.9296875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" ht="15.75">
       <c r="A1" s="4"/>
       <c r="B1" s="5" t="s">
         <v>3</v>
       </c>
       <c r="H1" s="23" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="I1" s="23"/>
       <c r="J1" s="23"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10">
       <c r="B2" s="24" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C2" s="24"/>
       <c r="D2" s="24"/>
       <c r="E2" s="24"/>
       <c r="H2" s="3"/>
       <c r="I2" s="19" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J2" s="17" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="H3" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="I3" s="17"/>
-      <c r="J3" s="17"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+        <v>17</v>
+      </c>
+      <c r="I3" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="J3" s="17">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="C4" s="16" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D4" s="31"/>
       <c r="E4" s="31"/>
       <c r="H4" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J4" s="3">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
       <c r="C5" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="22"/>
+      <c r="D5" s="22" t="s">
+        <v>30</v>
+      </c>
       <c r="E5" s="22"/>
       <c r="H5" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+        <v>19</v>
+      </c>
+      <c r="I5" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="J5" s="3">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
       <c r="B6" s="8"/>
       <c r="C6" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="22"/>
+      <c r="D6" s="37">
+        <v>46094</v>
+      </c>
       <c r="E6" s="22"/>
       <c r="F6" s="20"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10">
       <c r="B9" s="10" t="s">
         <v>4</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E9" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F9" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="F9" s="10" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B10" s="3">
+    </row>
+    <row r="10" spans="1:10" ht="57">
+      <c r="B10" s="38">
         <v>1</v>
       </c>
-      <c r="C10" s="1"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B11" s="3">
+      <c r="C10" s="38" t="s">
+        <v>74</v>
+      </c>
+      <c r="D10" s="39" t="s">
+        <v>61</v>
+      </c>
+      <c r="E10" s="39" t="s">
+        <v>65</v>
+      </c>
+      <c r="F10" s="39" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="42.75">
+      <c r="B11" s="38">
         <f>B10+1</f>
         <v>2</v>
       </c>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B12" s="3">
+      <c r="C11" s="38" t="s">
+        <v>75</v>
+      </c>
+      <c r="D11" s="39" t="s">
+        <v>62</v>
+      </c>
+      <c r="E11" s="39" t="s">
+        <v>66</v>
+      </c>
+      <c r="F11" s="39" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="42.75">
+      <c r="B12" s="38">
         <f t="shared" ref="B12:B30" si="0">B11+1</f>
         <v>3</v>
       </c>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B13" s="3">
+      <c r="C12" s="38" t="s">
+        <v>76</v>
+      </c>
+      <c r="D12" s="39" t="s">
+        <v>63</v>
+      </c>
+      <c r="E12" s="39" t="s">
+        <v>68</v>
+      </c>
+      <c r="F12" s="39" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="41.65">
+      <c r="B13" s="41">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="1"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B14" s="3">
+      <c r="C13" s="41" t="s">
+        <v>77</v>
+      </c>
+      <c r="D13" s="39" t="s">
+        <v>72</v>
+      </c>
+      <c r="E13" s="39" t="s">
+        <v>73</v>
+      </c>
+      <c r="F13" s="42" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="42.75">
+      <c r="B14" s="41">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="C14" s="1"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="C14" s="41" t="s">
+        <v>78</v>
+      </c>
+      <c r="D14" s="39" t="s">
+        <v>70</v>
+      </c>
+      <c r="E14" s="39" t="s">
+        <v>71</v>
+      </c>
+      <c r="F14" s="39" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
       <c r="B15" s="3">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -1731,7 +2671,7 @@
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:10">
       <c r="B16" s="3">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -1741,7 +2681,7 @@
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:6">
       <c r="B17" s="3">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -1751,7 +2691,7 @@
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:6">
       <c r="B18" s="3">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -1761,7 +2701,7 @@
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:6">
       <c r="B19" s="3">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -1771,7 +2711,7 @@
       <c r="E19" s="2"/>
       <c r="F19" s="2"/>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:6">
       <c r="B20" s="3">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -1781,7 +2721,7 @@
       <c r="E20" s="2"/>
       <c r="F20" s="2"/>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:6">
       <c r="B21" s="3">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -1791,7 +2731,7 @@
       <c r="E21" s="2"/>
       <c r="F21" s="2"/>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:6">
       <c r="B22" s="3">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -1801,7 +2741,7 @@
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:6">
       <c r="B23" s="3">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -1811,7 +2751,7 @@
       <c r="E23" s="2"/>
       <c r="F23" s="2"/>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:6">
       <c r="B24" s="3">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -1821,7 +2761,7 @@
       <c r="E24" s="2"/>
       <c r="F24" s="2"/>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:6">
       <c r="B25" s="3">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -1831,7 +2771,7 @@
       <c r="E25" s="2"/>
       <c r="F25" s="2"/>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:6">
       <c r="B26" s="3">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -1841,7 +2781,7 @@
       <c r="E26" s="2"/>
       <c r="F26" s="2"/>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:6">
       <c r="B27" s="3">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -1851,7 +2791,7 @@
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:6">
       <c r="B28" s="3">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -1861,7 +2801,7 @@
       <c r="E28" s="2"/>
       <c r="F28" s="2"/>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:6">
       <c r="B29" s="3">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -1871,7 +2811,7 @@
       <c r="E29" s="2"/>
       <c r="F29" s="2"/>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:6">
       <c r="B30" s="3">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -1881,15 +2821,17 @@
       <c r="E30" s="2"/>
       <c r="F30" s="2"/>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:6">
       <c r="C32" s="34" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D32" s="35"/>
       <c r="E32" s="35"/>
-      <c r="F32" s="18"/>
-    </row>
-    <row r="35" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F32" s="18" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="35" spans="6:6">
       <c r="F35" s="21"/>
     </row>
   </sheetData>

--- a/docs/Lab01/Lab01_ReviewReport.xlsx
+++ b/docs/Lab01/Lab01_ReviewReport.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ungur\OneDrive\Desktop\AN_3\SEM2\vvss\Lab01\CheckLists\CheckLists\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ungur\OneDrive\Desktop\AN_3\SEM2\vvss\Lab01\DrinkShop\repo_vvss_drinkshop\docs\Lab01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0641048-5E8C-492D-B2DC-51608FCDC6C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CD1B176-72F0-494B-97C7-9E21CC205936}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="650" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="650" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Requirements Phase Defects" sheetId="7" r:id="rId1"/>
@@ -170,9 +170,6 @@
     <t>Linia 25,36- FileAbstractRepository</t>
   </si>
   <si>
-    <t>Linia 16 - CsvEExporter</t>
-  </si>
-  <si>
     <t>A5</t>
   </si>
   <si>
@@ -189,583 +186,6 @@
   </si>
   <si>
     <t>Exceptii</t>
-  </si>
-  <si>
-    <t>Clasa Stoc este izolată și are doar un câmp de tip String pentru ingredient. Nu există o asociere clară în diagramă între Stoc și o entitate Ingredient. Imbunatatire: Crearea unei clase Ingredient și adăugarea unei relații de asociere (1 la 1) între Stoc și Ingredient.</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">La scăderea cantității din stoc la plasarea unei comenzi, se face un cast explicit la </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>(int)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="238"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> deși cantitatea este </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>double</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="238"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>s.setCantitate((int)(s.getCantitate() - deScazut));</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="238"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>). Asta duce la pierderea zecimalelor (ex: dacă se consumă 0.5 litri de lapte).Imbunatatire</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="238"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="238"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> eliminarea cast-ului la int. Cod corect: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>s.setCantitate(s.getCantitate() - deScazut);</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">În metodele </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>loadFromFile()</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="238"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> și </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>writeToFile()</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="238"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, excepțiile de tip </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>IOException</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="238"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> sunt doar printate în consolă (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>e.printStackTrace();</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="238"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>) și ascunse. Dacă fișierul nu poate fi scris/citit, programul continuă să ruleze corupt fără să avertizeze utilizatorul.Imbunatatire</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="238"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="238"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> aruncarea unei excepții pentru a opri execuția sau a notifica UI-ul: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>throw new RuntimeException(e);</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Căutarea produsului dintr-o comandă pentru a-l exporta se face folosind </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>.toList().get(0)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="238"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">. Dacă produsul a fost între timp șters din sistem, lista va fi goală și </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>.get(0)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="238"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> va arunca </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>IndexOutOfBoundsException</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="238"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>, crăpând aplicația. Imbunatatire</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="238"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="238"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> folosirea </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>.findFirst().orElse(null)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="238"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> și verificarea dacă produsul este null înainte de a scrie în CSV.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>În arhitectură este definită o singură excepție custom (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>ValidationException</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="238"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>). Nu există o strategie clară pentru erorile de persistență (ex: fișier lipsă, id duplicat). Imbunatatire</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="238"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="238"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Adăugarea unei clase </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>RepositoryException</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="238"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> pentru a separa erorile de validare de cele de persistență a datelor.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">TipBautura și </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>CategorieBautura</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="238"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> sunt modelate ca </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>Enum</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="238"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>. Conform cerințelor, utilizatorul trebuie să poată adăuga/șterge categorii la runtime, ceea ce este imposibil cu Enums. Imbnatatire</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="238"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="238"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Transformarea lor din </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>Enum</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="238"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> în </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>Clase</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="238"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (Entități) și crearea de Repository-uri pentru ele.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Nu se specifică ce se întâmplă dacă un produs comandat necesită mai multe ingrediente decât există momentan în stoc. Imbunatatire </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="238"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="238"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> aplicația va afișa eroare și va bloca comanda dacă stocul e insuficient</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Nu se specifică starea sistemului dacă fișierele text nu există. Imbunatatire</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="238"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="238"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> la prima rulare, dacă fișierele lipsesc, aplicația le va crea automat goale</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Se cere administrarea ingredientelor, dar lipsesc operațiile de bază.. Imbunatatire</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="238"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="238"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>ut</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="238"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>ilizatorul poate adăuga, modifica și șterge ingrediente</t>
-    </r>
   </si>
   <si>
     <t>0.75</t>
@@ -865,12 +285,51 @@
       <t>)</t>
     </r>
   </si>
+  <si>
+    <t>Aici problema este la actualizarea stocului dupa ce se plaseaza o comanda. Programul facea un cast la (int) pentru cantitatea ramasa, desi in clasa variabila este gandita ca double. Practic, daca avem ingrediente care se consuma cu zecimale (gen 0.5 litri de lapte la o cafea), cast-ul asta taie complet virgula, rotunjeste prost si strica toata evidenta stocului in timp. 
+Corectare: Am sters de tot cast-ul acela fortat ca sa las scaderea normala in virgula mobila. Linia a ramas asa: s.setCantitate(s.getCantitate() - deScazut);</t>
+  </si>
+  <si>
+    <t>In metodele care se ocupa cu salvarea si citirea din fisiere (loadFromFile si writeToFile), erorile de tip IOException erau prinse in blocul catch dar erau practic ignorate. Era pus doar un simplu e.printStackTrace(). Din cauza asta, daca fisierul nu exista sau nu avea permisiuni, aplicatia arunca niste text rosu in consola dar continua sa ruleze de parca totul e ok.
+Corectare: Am scos print-ul si am pus sa arunce eroarea mai departe ca sa crape aplicatia cum trebuie cand e o problema de fisier: throw new RuntimeException(e);</t>
+  </si>
+  <si>
+    <t>Linia 16 - CsvExporter</t>
+  </si>
+  <si>
+    <t>Cand se da export la raportul CSV, programul incearca sa extraga produsul dintr-o comanda folosind stream-uri si la final ia primul element cu .toList().get(0). Daca acel produs dintr-o comanda mai veche a fost sters intre timp din meniu, lista rezultata din filtru va fi goala. Cand apelezi get(0) pe ceva gol, crapa instant tot exportul cu IndexOutOfBoundsException.
+Corectare: Am inlocuit logica cu o metoda mai sigura pentru stream-uri. In loc de toList am folosit direct .findFirst().get().</t>
+  </si>
+  <si>
+    <t>TipBautura si CategorieBautura sunt trecute ca Enum-uri in diagrama, dar in cerinte scrie clar ca utilizatorul trebuie sa poata adauga sau sterge categorii noi direct din interfata. Nu ai cum sa faci asta dinamic cu un Enum pentru ca e hardcodat.
+Imbunatatire: Trebuie schimbate din Enum in clase normale (entitati) si facute repository-uri pentru ele ca sa le putem salva/modifica in fisiere.</t>
+  </si>
+  <si>
+    <t>Clasa Stoc este izolata in diagrama. In loc sa aiba o legatura cu o entitate de tip ingredient, are doar un simplu String pentru nume. Nu e ok pe partea de OOP pentru ca nu exista o asociere clara care sa ne arate asocierea dintre Stoc si Ingredient.
+Imbunatatire: Trebuie pusa o sageata de asociere in diagrama. Clasa Stoc trebuie sa fie legata direct printr-o relatie (1 la 1) de clasa IngredientReteta.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avem definita o singura clasa de exceptii (ValidationException). Asta inseamna ca daca pica citirea dintr-un fisier sau pui un ID duplicat, aplicatia arunca tot eroare de "validare", ceea ce nu are sens.
+Imbunatatire: Am adaugat in diagrama o clasa noua RepositoryException, ca sa separam logic erorile date de date gresite de alea date de fisierele care crapa. </t>
+  </si>
+  <si>
+    <t>In documentul cu cerinte se zice ca stocul se actualizeaza cand se fac comenzi, dar nu scrie absolut nicaieri ce se intampla daca cineva vrea sa comande o bautura si nu mai avem destule ingrediente. Cum e scris acum, programul ar putea sa scada pe minus fara sa ne avertizeze.
+Imbunatatire: Trebuie adaugata o regula clara: "La plasarea unei comenzi, aplicația trebuie să verifice dacă există suficiente ingrediente în stoc pentru prepararea produselor comandate. Dacă stocul este insuficient, aplicația va afișa un mesaj de eroare și nu va permite finalizarea comenzii."</t>
+  </si>
+  <si>
+    <t>La inceputul PDF-ului scrie ca aplicatia este pentru gestionarea ingredientelor, dar in lista de functionalitati zice doar de afisare stoc si actualizare. Nu zice nimic de cum adaugi un ingredient nou in sistem sau cum ii schimbi numele. Lipsesc practic operatiile de baza (CRUD).
+Imbunatatire: Am adaugat cerinte noi: "Aplicația trebuie să permită gestionarea ingredientelor: adăugare ingredient nou; modificare ingredient existent; ștergere ingredient; afișare listă ingrediente."</t>
+  </si>
+  <si>
+    <t>La sectiunea de cerinte non-functionale zice doar ca salvarea datelor se face in fisiere text, dar nu clarifica deloc starea initiala a sistemului. Daca fisierele alea txt nu exista in folder, aplicatia o sa dea eroare la pornire sau stie sa si le creeze singura?
+Imbunatatire: Am completat cerintele cu mentiunea: "La prima rulare a aplicației, dacă fișierele de date necesare nu există, aplicația va crea automat fișiere goale pentru stocarea datelor (produse, ingrediente, rețete și comenzi)."</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -954,28 +413,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="238"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="238"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial Unicode MS"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1085,7 +522,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1116,6 +553,19 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1157,23 +607,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1483,36 +916,36 @@
     <tabColor theme="7" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="A1:J27"/>
-  <sheetFormatPr defaultColWidth="8.9296875" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.9296875" style="6"/>
-    <col min="2" max="2" width="12.265625" style="6" customWidth="1"/>
-    <col min="3" max="4" width="16.265625" style="6" customWidth="1"/>
-    <col min="5" max="5" width="67.59765625" style="6" customWidth="1"/>
-    <col min="6" max="8" width="8.9296875" style="6"/>
+    <col min="1" max="1" width="9" style="6"/>
+    <col min="2" max="2" width="12.28515625" style="6" customWidth="1"/>
+    <col min="3" max="4" width="16.28515625" style="6" customWidth="1"/>
+    <col min="5" max="5" width="67.5703125" style="6" customWidth="1"/>
+    <col min="6" max="8" width="9" style="6"/>
     <col min="9" max="9" width="21" style="6" customWidth="1"/>
-    <col min="10" max="10" width="14.46484375" style="6" customWidth="1"/>
-    <col min="11" max="16384" width="8.9296875" style="6"/>
+    <col min="10" max="10" width="14.42578125" style="6" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.75">
+    <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="4"/>
       <c r="B1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="23" t="s">
+      <c r="H1" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="I1" s="23"/>
-      <c r="J1" s="23"/>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="B2" s="24" t="s">
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B2" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
       <c r="H2" s="3"/>
       <c r="I2" s="19" t="s">
         <v>27</v>
@@ -1521,7 +954,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="H3" s="17" t="s">
         <v>17</v>
       </c>
@@ -1532,14 +965,14 @@
         <v>237</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C4" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="25" t="s">
+      <c r="D4" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="25"/>
+      <c r="E4" s="30"/>
       <c r="H4" s="17" t="s">
         <v>18</v>
       </c>
@@ -1550,44 +983,44 @@
         <v>237</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C5" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="26" t="s">
+      <c r="D5" s="31" t="s">
         <v>30</v>
       </c>
-      <c r="E5" s="27"/>
+      <c r="E5" s="32"/>
       <c r="H5" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="I5" s="36" t="s">
+      <c r="I5" s="22" t="s">
         <v>31</v>
       </c>
       <c r="J5" s="3">
         <v>237</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B6" s="8"/>
       <c r="C6" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="22" t="s">
+      <c r="D6" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="E6" s="22"/>
-    </row>
-    <row r="7" spans="1:10">
+      <c r="E6" s="27"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C7" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="37">
+      <c r="D7" s="26">
         <v>46094</v>
       </c>
-      <c r="E7" s="22"/>
-    </row>
-    <row r="9" spans="1:10">
+      <c r="E7" s="27"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B9" s="10" t="s">
         <v>4</v>
       </c>
@@ -1601,51 +1034,51 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="42.75">
-      <c r="B10" s="38">
+    <row r="10" spans="1:10" ht="135" x14ac:dyDescent="0.25">
+      <c r="B10" s="23">
         <v>1</v>
       </c>
-      <c r="C10" s="39" t="s">
+      <c r="C10" s="24" t="s">
         <v>34</v>
       </c>
-      <c r="D10" s="40" t="s">
+      <c r="D10" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="E10" s="39" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="28.5">
-      <c r="B11" s="38">
+      <c r="E10" s="24" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="105" x14ac:dyDescent="0.25">
+      <c r="B11" s="23">
         <f>B10+1</f>
         <v>2</v>
       </c>
-      <c r="C11" s="38" t="s">
+      <c r="C11" s="23" t="s">
         <v>35</v>
       </c>
-      <c r="D11" s="38" t="s">
+      <c r="D11" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="E11" s="39" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="28.5">
-      <c r="B12" s="38">
+      <c r="E11" s="24" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="120" x14ac:dyDescent="0.25">
+      <c r="B12" s="23">
         <f t="shared" ref="B12:B25" si="0">B11+1</f>
         <v>3</v>
       </c>
-      <c r="C12" s="38" t="s">
+      <c r="C12" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="D12" s="38" t="s">
+      <c r="D12" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="E12" s="39" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
+      <c r="E12" s="24" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B13" s="3">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -1654,7 +1087,7 @@
       <c r="D13" s="1"/>
       <c r="E13" s="2"/>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B14" s="3">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -1663,7 +1096,7 @@
       <c r="D14" s="1"/>
       <c r="E14" s="2"/>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B15" s="3">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -1672,7 +1105,7 @@
       <c r="D15" s="1"/>
       <c r="E15" s="2"/>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B16" s="3">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -1681,7 +1114,7 @@
       <c r="D16" s="1"/>
       <c r="E16" s="2"/>
     </row>
-    <row r="17" spans="2:5">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B17" s="3">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -1690,7 +1123,7 @@
       <c r="D17" s="1"/>
       <c r="E17" s="2"/>
     </row>
-    <row r="18" spans="2:5">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B18" s="3">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -1699,7 +1132,7 @@
       <c r="D18" s="3"/>
       <c r="E18" s="15"/>
     </row>
-    <row r="19" spans="2:5">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B19" s="3">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -1708,7 +1141,7 @@
       <c r="D19" s="3"/>
       <c r="E19" s="15"/>
     </row>
-    <row r="20" spans="2:5">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B20" s="3">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -1717,7 +1150,7 @@
       <c r="D20" s="3"/>
       <c r="E20" s="15"/>
     </row>
-    <row r="21" spans="2:5">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B21" s="3">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -1726,7 +1159,7 @@
       <c r="D21" s="3"/>
       <c r="E21" s="15"/>
     </row>
-    <row r="22" spans="2:5">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B22" s="3">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -1735,7 +1168,7 @@
       <c r="D22" s="3"/>
       <c r="E22" s="15"/>
     </row>
-    <row r="23" spans="2:5">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B23" s="3">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -1744,7 +1177,7 @@
       <c r="D23" s="3"/>
       <c r="E23" s="15"/>
     </row>
-    <row r="24" spans="2:5">
+    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B24" s="3">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -1753,7 +1186,7 @@
       <c r="D24" s="3"/>
       <c r="E24" s="15"/>
     </row>
-    <row r="25" spans="2:5">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B25" s="3">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -1762,7 +1195,7 @@
       <c r="D25" s="3"/>
       <c r="E25" s="15"/>
     </row>
-    <row r="27" spans="2:5">
+    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C27" s="11" t="s">
         <v>8</v>
       </c>
@@ -1791,35 +1224,35 @@
     <tabColor theme="9" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="A1:J28"/>
-  <sheetFormatPr defaultColWidth="8.9296875" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.9296875" style="6"/>
-    <col min="2" max="2" width="12.265625" style="6" customWidth="1"/>
-    <col min="3" max="4" width="16.265625" style="6" customWidth="1"/>
-    <col min="5" max="5" width="41.46484375" style="6" customWidth="1"/>
-    <col min="6" max="8" width="8.9296875" style="6"/>
-    <col min="9" max="9" width="22.06640625" style="6" customWidth="1"/>
-    <col min="10" max="16384" width="8.9296875" style="6"/>
+    <col min="1" max="1" width="9" style="6"/>
+    <col min="2" max="2" width="12.28515625" style="6" customWidth="1"/>
+    <col min="3" max="4" width="16.28515625" style="6" customWidth="1"/>
+    <col min="5" max="5" width="41.42578125" style="6" customWidth="1"/>
+    <col min="6" max="8" width="9" style="6"/>
+    <col min="9" max="9" width="22" style="6" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.75">
+    <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="4"/>
       <c r="B1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="23" t="s">
+      <c r="H1" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="I1" s="23"/>
-      <c r="J1" s="23"/>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="B2" s="24" t="s">
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B2" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
       <c r="H2" s="3"/>
       <c r="I2" s="19" t="s">
         <v>27</v>
@@ -1828,7 +1261,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="H3" s="17" t="s">
         <v>17</v>
       </c>
@@ -1839,14 +1272,14 @@
         <v>237</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C4" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="28" t="s">
+      <c r="D4" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="28"/>
+      <c r="E4" s="33"/>
       <c r="H4" s="17" t="s">
         <v>18</v>
       </c>
@@ -1857,44 +1290,44 @@
         <v>237</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C5" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="29" t="s">
+      <c r="D5" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="E5" s="30"/>
+      <c r="E5" s="35"/>
       <c r="H5" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="I5" s="36" t="s">
+      <c r="I5" s="22" t="s">
         <v>31</v>
       </c>
       <c r="J5" s="3">
         <v>237</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B6" s="8"/>
       <c r="C6" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="22" t="s">
+      <c r="D6" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="E6" s="22"/>
-    </row>
-    <row r="7" spans="1:10">
+      <c r="E6" s="27"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C7" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="37">
+      <c r="D7" s="26">
         <v>46094</v>
       </c>
-      <c r="E7" s="22"/>
-    </row>
-    <row r="9" spans="1:10">
+      <c r="E7" s="27"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B9" s="10" t="s">
         <v>4</v>
       </c>
@@ -1908,51 +1341,51 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="85.5">
-      <c r="B10" s="38">
+    <row r="10" spans="1:10" ht="135" x14ac:dyDescent="0.25">
+      <c r="B10" s="23">
         <v>1</v>
       </c>
-      <c r="C10" s="38" t="s">
-        <v>45</v>
-      </c>
-      <c r="D10" s="39" t="s">
-        <v>50</v>
-      </c>
-      <c r="E10" s="39" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="85.5">
-      <c r="B11" s="38">
+      <c r="C10" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="D10" s="24" t="s">
+        <v>49</v>
+      </c>
+      <c r="E10" s="24" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="150" x14ac:dyDescent="0.25">
+      <c r="B11" s="23">
         <f>B10+1</f>
         <v>2</v>
       </c>
-      <c r="C11" s="38" t="s">
-        <v>46</v>
-      </c>
-      <c r="D11" s="39" t="s">
-        <v>49</v>
-      </c>
-      <c r="E11" s="39" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="85.5">
-      <c r="B12" s="38">
+      <c r="C11" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="D11" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="E11" s="24" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="150" x14ac:dyDescent="0.25">
+      <c r="B12" s="23">
         <f t="shared" ref="B12:B26" si="0">B11+1</f>
         <v>3</v>
       </c>
-      <c r="C12" s="38" t="s">
+      <c r="C12" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="D12" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="D12" s="38" t="s">
-        <v>48</v>
-      </c>
-      <c r="E12" s="39" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
+      <c r="E12" s="24" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B13" s="3">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -1961,7 +1394,7 @@
       <c r="D13" s="1"/>
       <c r="E13" s="2"/>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B14" s="3">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -1970,7 +1403,7 @@
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B15" s="3">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -1979,7 +1412,7 @@
       <c r="D15" s="1"/>
       <c r="E15" s="2"/>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B16" s="3">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -1988,7 +1421,7 @@
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
     </row>
-    <row r="17" spans="2:5">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B17" s="3">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -1997,7 +1430,7 @@
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
     </row>
-    <row r="18" spans="2:5">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B18" s="3">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -2006,7 +1439,7 @@
       <c r="D18" s="1"/>
       <c r="E18" s="2"/>
     </row>
-    <row r="19" spans="2:5">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B19" s="3">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -2015,7 +1448,7 @@
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
     </row>
-    <row r="20" spans="2:5">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B20" s="3">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -2024,7 +1457,7 @@
       <c r="D20" s="1"/>
       <c r="E20" s="2"/>
     </row>
-    <row r="21" spans="2:5">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B21" s="3">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -2033,7 +1466,7 @@
       <c r="D21" s="1"/>
       <c r="E21" s="2"/>
     </row>
-    <row r="22" spans="2:5">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B22" s="3">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -2042,7 +1475,7 @@
       <c r="D22" s="1"/>
       <c r="E22" s="2"/>
     </row>
-    <row r="23" spans="2:5">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B23" s="3">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -2051,7 +1484,7 @@
       <c r="D23" s="1"/>
       <c r="E23" s="2"/>
     </row>
-    <row r="24" spans="2:5">
+    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B24" s="3">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -2060,7 +1493,7 @@
       <c r="D24" s="1"/>
       <c r="E24" s="2"/>
     </row>
-    <row r="25" spans="2:5">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B25" s="3">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -2069,7 +1502,7 @@
       <c r="D25" s="1"/>
       <c r="E25" s="2"/>
     </row>
-    <row r="26" spans="2:5">
+    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B26" s="3">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -2078,7 +1511,7 @@
       <c r="D26" s="1"/>
       <c r="E26" s="2"/>
     </row>
-    <row r="28" spans="2:5">
+    <row r="28" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C28" s="11" t="s">
         <v>8</v>
       </c>
@@ -2107,36 +1540,36 @@
     <tabColor theme="3" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="A1:J32"/>
-  <sheetFormatPr defaultColWidth="8.9296875" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.9296875" style="6"/>
-    <col min="2" max="2" width="12.265625" style="6" customWidth="1"/>
-    <col min="3" max="3" width="16.265625" style="6" customWidth="1"/>
+    <col min="1" max="1" width="9" style="6"/>
+    <col min="2" max="2" width="12.28515625" style="6" customWidth="1"/>
+    <col min="3" max="3" width="16.28515625" style="6" customWidth="1"/>
     <col min="4" max="4" width="18" style="6" customWidth="1"/>
-    <col min="5" max="5" width="41.46484375" style="6" customWidth="1"/>
-    <col min="6" max="8" width="8.9296875" style="6"/>
-    <col min="9" max="9" width="26.73046875" style="6" customWidth="1"/>
-    <col min="10" max="16384" width="8.9296875" style="6"/>
+    <col min="5" max="5" width="41.42578125" style="6" customWidth="1"/>
+    <col min="6" max="8" width="9" style="6"/>
+    <col min="9" max="9" width="26.7109375" style="6" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.75">
+    <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="4"/>
       <c r="B1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="23" t="s">
+      <c r="H1" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="I1" s="23"/>
-      <c r="J1" s="23"/>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="B2" s="24" t="s">
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B2" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
       <c r="H2" s="3"/>
       <c r="I2" s="19" t="s">
         <v>27</v>
@@ -2145,7 +1578,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="H3" s="17" t="s">
         <v>17</v>
       </c>
@@ -2156,14 +1589,14 @@
         <v>237</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C4" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="31" t="s">
+      <c r="D4" s="36" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="31"/>
+      <c r="E4" s="36"/>
       <c r="H4" s="17" t="s">
         <v>18</v>
       </c>
@@ -2174,44 +1607,44 @@
         <v>237</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C5" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="32" t="s">
+      <c r="D5" s="37" t="s">
         <v>30</v>
       </c>
-      <c r="E5" s="33"/>
+      <c r="E5" s="38"/>
       <c r="H5" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="I5" s="36" t="s">
+      <c r="I5" s="22" t="s">
         <v>31</v>
       </c>
       <c r="J5" s="3">
         <v>237</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B6" s="8"/>
       <c r="C6" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="22" t="s">
+      <c r="D6" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="E6" s="22"/>
-    </row>
-    <row r="7" spans="1:10">
+      <c r="E6" s="27"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C7" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="37">
+      <c r="D7" s="26">
         <v>46094</v>
       </c>
-      <c r="E7" s="22"/>
-    </row>
-    <row r="9" spans="1:10">
+      <c r="E7" s="27"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B9" s="10" t="s">
         <v>4</v>
       </c>
@@ -2225,51 +1658,51 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="126.75">
-      <c r="B10" s="38">
+    <row r="10" spans="1:10" ht="195" x14ac:dyDescent="0.25">
+      <c r="B10" s="24">
         <v>1</v>
       </c>
-      <c r="C10" s="38" t="s">
+      <c r="C10" s="24" t="s">
         <v>40</v>
       </c>
-      <c r="D10" s="39" t="s">
+      <c r="D10" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="E10" s="39" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="112.5">
-      <c r="B11" s="38">
+      <c r="E10" s="24" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="195" x14ac:dyDescent="0.25">
+      <c r="B11" s="24">
         <f>B10+1</f>
         <v>2</v>
       </c>
-      <c r="C11" s="38" t="s">
+      <c r="C11" s="24" t="s">
         <v>41</v>
       </c>
-      <c r="D11" s="38" t="s">
+      <c r="D11" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E11" s="39" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="114">
-      <c r="B12" s="38">
+      <c r="E11" s="24" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="180" x14ac:dyDescent="0.25">
+      <c r="B12" s="24">
         <f t="shared" ref="B12:B30" si="0">B11+1</f>
         <v>3</v>
       </c>
-      <c r="C12" s="38" t="s">
+      <c r="C12" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="D12" s="38" t="s">
-        <v>44</v>
-      </c>
-      <c r="E12" s="39" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
+      <c r="D12" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="E12" s="24" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B13" s="3">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -2278,7 +1711,7 @@
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B14" s="3">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -2287,7 +1720,7 @@
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B15" s="3">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -2296,7 +1729,7 @@
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B16" s="3">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -2305,7 +1738,7 @@
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
     </row>
-    <row r="17" spans="2:5">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B17" s="3">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -2314,7 +1747,7 @@
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
     </row>
-    <row r="18" spans="2:5">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B18" s="3">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -2323,7 +1756,7 @@
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
     </row>
-    <row r="19" spans="2:5">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B19" s="3">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -2332,7 +1765,7 @@
       <c r="D19" s="1"/>
       <c r="E19" s="2"/>
     </row>
-    <row r="20" spans="2:5">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B20" s="3">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -2341,7 +1774,7 @@
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
     </row>
-    <row r="21" spans="2:5">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B21" s="3">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -2350,7 +1783,7 @@
       <c r="D21" s="1"/>
       <c r="E21" s="2"/>
     </row>
-    <row r="22" spans="2:5">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B22" s="3">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -2359,7 +1792,7 @@
       <c r="D22" s="2"/>
       <c r="E22" s="2"/>
     </row>
-    <row r="23" spans="2:5">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B23" s="3">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -2368,7 +1801,7 @@
       <c r="D23" s="2"/>
       <c r="E23" s="2"/>
     </row>
-    <row r="24" spans="2:5">
+    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B24" s="3">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -2377,7 +1810,7 @@
       <c r="D24" s="2"/>
       <c r="E24" s="2"/>
     </row>
-    <row r="25" spans="2:5">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B25" s="3">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -2386,7 +1819,7 @@
       <c r="D25" s="2"/>
       <c r="E25" s="2"/>
     </row>
-    <row r="26" spans="2:5">
+    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B26" s="3">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -2395,7 +1828,7 @@
       <c r="D26" s="1"/>
       <c r="E26" s="2"/>
     </row>
-    <row r="27" spans="2:5">
+    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B27" s="3">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -2404,7 +1837,7 @@
       <c r="D27" s="2"/>
       <c r="E27" s="1"/>
     </row>
-    <row r="28" spans="2:5">
+    <row r="28" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B28" s="3">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -2413,7 +1846,7 @@
       <c r="D28" s="2"/>
       <c r="E28" s="2"/>
     </row>
-    <row r="29" spans="2:5">
+    <row r="29" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B29" s="3">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -2422,7 +1855,7 @@
       <c r="D29" s="2"/>
       <c r="E29" s="2"/>
     </row>
-    <row r="30" spans="2:5">
+    <row r="30" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B30" s="3">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -2431,7 +1864,7 @@
       <c r="D30" s="2"/>
       <c r="E30" s="2"/>
     </row>
-    <row r="32" spans="2:5">
+    <row r="32" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C32" s="11" t="s">
         <v>8</v>
       </c>
@@ -2460,37 +1893,37 @@
     <tabColor theme="6" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:J35"/>
-  <sheetFormatPr defaultColWidth="8.9296875" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.9296875" style="6"/>
-    <col min="2" max="2" width="12.265625" style="6" customWidth="1"/>
-    <col min="3" max="3" width="16.265625" style="6" customWidth="1"/>
+    <col min="1" max="1" width="9" style="6"/>
+    <col min="2" max="2" width="12.28515625" style="6" customWidth="1"/>
+    <col min="3" max="3" width="16.28515625" style="6" customWidth="1"/>
     <col min="4" max="4" width="18" style="6" customWidth="1"/>
-    <col min="5" max="5" width="23.9296875" style="6" customWidth="1"/>
-    <col min="6" max="6" width="16.59765625" style="6" customWidth="1"/>
-    <col min="7" max="8" width="8.9296875" style="6"/>
-    <col min="9" max="9" width="26.73046875" style="6" customWidth="1"/>
-    <col min="10" max="16384" width="8.9296875" style="6"/>
+    <col min="5" max="5" width="24" style="6" customWidth="1"/>
+    <col min="6" max="6" width="16.5703125" style="6" customWidth="1"/>
+    <col min="7" max="8" width="9" style="6"/>
+    <col min="9" max="9" width="26.7109375" style="6" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.75">
+    <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="4"/>
       <c r="B1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="23" t="s">
+      <c r="H1" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="I1" s="23"/>
-      <c r="J1" s="23"/>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="B2" s="24" t="s">
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B2" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
       <c r="H2" s="3"/>
       <c r="I2" s="19" t="s">
         <v>27</v>
@@ -2499,7 +1932,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="H3" s="17" t="s">
         <v>17</v>
       </c>
@@ -2510,12 +1943,12 @@
         <v>237</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C4" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="31"/>
-      <c r="E4" s="31"/>
+      <c r="D4" s="36"/>
+      <c r="E4" s="36"/>
       <c r="H4" s="17" t="s">
         <v>18</v>
       </c>
@@ -2526,36 +1959,36 @@
         <v>237</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C5" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="22" t="s">
+      <c r="D5" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="E5" s="22"/>
+      <c r="E5" s="27"/>
       <c r="H5" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="I5" s="36" t="s">
+      <c r="I5" s="22" t="s">
         <v>31</v>
       </c>
       <c r="J5" s="3">
         <v>237</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B6" s="8"/>
       <c r="C6" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="37">
+      <c r="D6" s="26">
         <v>46094</v>
       </c>
-      <c r="E6" s="22"/>
+      <c r="E6" s="27"/>
       <c r="F6" s="20"/>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B9" s="10" t="s">
         <v>4</v>
       </c>
@@ -2572,96 +2005,96 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="57">
-      <c r="B10" s="38">
+    <row r="10" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="B10" s="24">
         <v>1</v>
       </c>
-      <c r="C10" s="38" t="s">
-        <v>74</v>
-      </c>
-      <c r="D10" s="39" t="s">
-        <v>61</v>
-      </c>
-      <c r="E10" s="39" t="s">
-        <v>65</v>
-      </c>
-      <c r="F10" s="39" t="s">
+      <c r="C10" s="24" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" ht="42.75">
-      <c r="B11" s="38">
+      <c r="D10" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="E10" s="24" t="s">
+        <v>55</v>
+      </c>
+      <c r="F10" s="24" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="B11" s="24">
         <f>B10+1</f>
         <v>2</v>
       </c>
-      <c r="C11" s="38" t="s">
-        <v>75</v>
-      </c>
-      <c r="D11" s="39" t="s">
-        <v>62</v>
-      </c>
-      <c r="E11" s="39" t="s">
-        <v>66</v>
-      </c>
-      <c r="F11" s="39" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="42.75">
-      <c r="B12" s="38">
+      <c r="C11" s="24" t="s">
+        <v>65</v>
+      </c>
+      <c r="D11" s="24" t="s">
+        <v>52</v>
+      </c>
+      <c r="E11" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="F11" s="24" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="B12" s="24">
         <f t="shared" ref="B12:B30" si="0">B11+1</f>
         <v>3</v>
       </c>
-      <c r="C12" s="38" t="s">
-        <v>76</v>
-      </c>
-      <c r="D12" s="39" t="s">
+      <c r="C12" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="D12" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="E12" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="F12" s="24" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+      <c r="B13" s="24">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="C13" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="D13" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="E13" s="24" t="s">
         <v>63</v>
       </c>
-      <c r="E12" s="39" t="s">
+      <c r="F13" s="24" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="B14" s="24">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="C14" s="24" t="s">
         <v>68</v>
       </c>
-      <c r="F12" s="39" t="s">
+      <c r="D14" s="24" t="s">
+        <v>60</v>
+      </c>
+      <c r="E14" s="24" t="s">
+        <v>61</v>
+      </c>
+      <c r="F14" s="24" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="41.65">
-      <c r="B13" s="41">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="C13" s="41" t="s">
-        <v>77</v>
-      </c>
-      <c r="D13" s="39" t="s">
-        <v>72</v>
-      </c>
-      <c r="E13" s="39" t="s">
-        <v>73</v>
-      </c>
-      <c r="F13" s="42" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="42.75">
-      <c r="B14" s="41">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="C14" s="41" t="s">
-        <v>78</v>
-      </c>
-      <c r="D14" s="39" t="s">
-        <v>70</v>
-      </c>
-      <c r="E14" s="39" t="s">
-        <v>71</v>
-      </c>
-      <c r="F14" s="39" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B15" s="3">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -2671,7 +2104,7 @@
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B16" s="3">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -2681,7 +2114,7 @@
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
     </row>
-    <row r="17" spans="2:6">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B17" s="3">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -2691,7 +2124,7 @@
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
     </row>
-    <row r="18" spans="2:6">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B18" s="3">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -2701,7 +2134,7 @@
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
     </row>
-    <row r="19" spans="2:6">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B19" s="3">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -2711,7 +2144,7 @@
       <c r="E19" s="2"/>
       <c r="F19" s="2"/>
     </row>
-    <row r="20" spans="2:6">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B20" s="3">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -2721,7 +2154,7 @@
       <c r="E20" s="2"/>
       <c r="F20" s="2"/>
     </row>
-    <row r="21" spans="2:6">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B21" s="3">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -2731,7 +2164,7 @@
       <c r="E21" s="2"/>
       <c r="F21" s="2"/>
     </row>
-    <row r="22" spans="2:6">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B22" s="3">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -2741,7 +2174,7 @@
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
     </row>
-    <row r="23" spans="2:6">
+    <row r="23" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B23" s="3">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -2751,7 +2184,7 @@
       <c r="E23" s="2"/>
       <c r="F23" s="2"/>
     </row>
-    <row r="24" spans="2:6">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B24" s="3">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -2761,7 +2194,7 @@
       <c r="E24" s="2"/>
       <c r="F24" s="2"/>
     </row>
-    <row r="25" spans="2:6">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B25" s="3">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -2771,7 +2204,7 @@
       <c r="E25" s="2"/>
       <c r="F25" s="2"/>
     </row>
-    <row r="26" spans="2:6">
+    <row r="26" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B26" s="3">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -2781,7 +2214,7 @@
       <c r="E26" s="2"/>
       <c r="F26" s="2"/>
     </row>
-    <row r="27" spans="2:6">
+    <row r="27" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B27" s="3">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -2791,7 +2224,7 @@
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
     </row>
-    <row r="28" spans="2:6">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B28" s="3">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -2801,7 +2234,7 @@
       <c r="E28" s="2"/>
       <c r="F28" s="2"/>
     </row>
-    <row r="29" spans="2:6">
+    <row r="29" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B29" s="3">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -2811,7 +2244,7 @@
       <c r="E29" s="2"/>
       <c r="F29" s="2"/>
     </row>
-    <row r="30" spans="2:6">
+    <row r="30" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B30" s="3">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -2821,17 +2254,17 @@
       <c r="E30" s="2"/>
       <c r="F30" s="2"/>
     </row>
-    <row r="32" spans="2:6">
-      <c r="C32" s="34" t="s">
+    <row r="32" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C32" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="D32" s="35"/>
-      <c r="E32" s="35"/>
+      <c r="D32" s="40"/>
+      <c r="E32" s="40"/>
       <c r="F32" s="18" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="35" spans="6:6">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="35" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F35" s="21"/>
     </row>
   </sheetData>

--- a/docs/Lab01/Lab01_ReviewReport.xlsx
+++ b/docs/Lab01/Lab01_ReviewReport.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ungur\OneDrive\Desktop\AN_3\SEM2\vvss\Lab01\DrinkShop\repo_vvss_drinkshop\docs\Lab01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CD1B176-72F0-494B-97C7-9E21CC205936}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F19FE688-FCF0-41C6-BF88-D7E6258CF6E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="650" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -305,10 +305,6 @@
 Imbunatatire: Trebuie schimbate din Enum in clase normale (entitati) si facute repository-uri pentru ele ca sa le putem salva/modifica in fisiere.</t>
   </si>
   <si>
-    <t>Clasa Stoc este izolata in diagrama. In loc sa aiba o legatura cu o entitate de tip ingredient, are doar un simplu String pentru nume. Nu e ok pe partea de OOP pentru ca nu exista o asociere clara care sa ne arate asocierea dintre Stoc si Ingredient.
-Imbunatatire: Trebuie pusa o sageata de asociere in diagrama. Clasa Stoc trebuie sa fie legata direct printr-o relatie (1 la 1) de clasa IngredientReteta.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Avem definita o singura clasa de exceptii (ValidationException). Asta inseamna ca daca pica citirea dintr-un fisier sau pui un ID duplicat, aplicatia arunca tot eroare de "validare", ceea ce nu are sens.
 Imbunatatire: Am adaugat in diagrama o clasa noua RepositoryException, ca sa separam logic erorile date de date gresite de alea date de fisierele care crapa. </t>
   </si>
@@ -323,6 +319,10 @@
   <si>
     <t>La sectiunea de cerinte non-functionale zice doar ca salvarea datelor se face in fisiere text, dar nu clarifica deloc starea initiala a sistemului. Daca fisierele alea txt nu exista in folder, aplicatia o sa dea eroare la pornire sau stie sa si le creeze singura?
 Imbunatatire: Am completat cerintele cu mentiunea: "La prima rulare a aplicației, dacă fișierele de date necesare nu există, aplicația va crea automat fișiere goale pentru stocarea datelor (produse, ingrediente, rețete și comenzi)."</t>
+  </si>
+  <si>
+    <t>Clasa Stoc este izolata in diagrama. In loc sa aiba o legatura cu o entitate de tip ingredient, are doar un simplu String pentru nume. Nu e ok pe partea de OOP pentru ca nu exista o asociere clara care sa ne arate legatura dintre Stoc si Ingredient.
+Imbunatatire: Trebuie creata o clasa noua numita Ingredient in diagrama, si pusa o sageata de asociere intre ele. Practic, clasa Stoc trebuie sa fie legata direct printr-o relatie (1 la 1) de aceasta noua clasa Ingredient.</t>
   </si>
 </sst>
 </file>
@@ -921,7 +921,7 @@
     <col min="1" max="1" width="9" style="6"/>
     <col min="2" max="2" width="12.28515625" style="6" customWidth="1"/>
     <col min="3" max="4" width="16.28515625" style="6" customWidth="1"/>
-    <col min="5" max="5" width="67.5703125" style="6" customWidth="1"/>
+    <col min="5" max="5" width="54.5703125" style="6" customWidth="1"/>
     <col min="6" max="8" width="9" style="6"/>
     <col min="9" max="9" width="21" style="6" customWidth="1"/>
     <col min="10" max="10" width="14.42578125" style="6" customWidth="1"/>
@@ -1034,7 +1034,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="135" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" ht="165" x14ac:dyDescent="0.25">
       <c r="B10" s="23">
         <v>1</v>
       </c>
@@ -1045,10 +1045,10 @@
         <v>37</v>
       </c>
       <c r="E10" s="24" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="105" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="135" x14ac:dyDescent="0.25">
       <c r="B11" s="23">
         <f>B10+1</f>
         <v>2</v>
@@ -1060,10 +1060,10 @@
         <v>37</v>
       </c>
       <c r="E11" s="24" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="120" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="150" x14ac:dyDescent="0.25">
       <c r="B12" s="23">
         <f t="shared" ref="B12:B25" si="0">B11+1</f>
         <v>3</v>
@@ -1075,7 +1075,7 @@
         <v>37</v>
       </c>
       <c r="E12" s="24" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
@@ -1352,10 +1352,10 @@
         <v>49</v>
       </c>
       <c r="E10" s="24" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="150" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="180" x14ac:dyDescent="0.25">
       <c r="B11" s="23">
         <f>B10+1</f>
         <v>2</v>
@@ -1367,7 +1367,7 @@
         <v>48</v>
       </c>
       <c r="E11" s="24" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="150" x14ac:dyDescent="0.25">

--- a/docs/Lab01/Lab01_ReviewReport.xlsx
+++ b/docs/Lab01/Lab01_ReviewReport.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ungur\OneDrive\Desktop\AN_3\SEM2\vvss\Lab01\DrinkShop\repo_vvss_drinkshop\docs\Lab01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F19FE688-FCF0-41C6-BF88-D7E6258CF6E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06347216-CCBF-411A-BFA1-17D30F729F9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="650" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="24196" windowHeight="14476" tabRatio="650" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Requirements Phase Defects" sheetId="7" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="82">
   <si>
     <t>Document  Title:</t>
   </si>
@@ -323,6 +323,9 @@
   <si>
     <t>Clasa Stoc este izolata in diagrama. In loc sa aiba o legatura cu o entitate de tip ingredient, are doar un simplu String pentru nume. Nu e ok pe partea de OOP pentru ca nu exista o asociere clara care sa ne arate legatura dintre Stoc si Ingredient.
 Imbunatatire: Trebuie creata o clasa noua numita Ingredient in diagrama, si pusa o sageata de asociere intre ele. Practic, clasa Stoc trebuie sa fie legata direct printr-o relatie (1 la 1) de aceasta noua clasa Ingredient.</t>
+  </si>
+  <si>
+    <t>h</t>
   </si>
 </sst>
 </file>
@@ -572,8 +575,17 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -591,15 +603,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -916,19 +919,19 @@
     <tabColor theme="7" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="A1:J27"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="9" style="6"/>
-    <col min="2" max="2" width="12.28515625" style="6" customWidth="1"/>
-    <col min="3" max="4" width="16.28515625" style="6" customWidth="1"/>
-    <col min="5" max="5" width="54.5703125" style="6" customWidth="1"/>
+    <col min="2" max="2" width="12.265625" style="6" customWidth="1"/>
+    <col min="3" max="4" width="16.265625" style="6" customWidth="1"/>
+    <col min="5" max="5" width="54.59765625" style="6" customWidth="1"/>
     <col min="6" max="8" width="9" style="6"/>
     <col min="9" max="9" width="21" style="6" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="6" customWidth="1"/>
+    <col min="10" max="10" width="14.3984375" style="6" customWidth="1"/>
     <col min="11" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A1" s="4"/>
       <c r="B1" s="5" t="s">
         <v>3</v>
@@ -939,13 +942,13 @@
       <c r="I1" s="28"/>
       <c r="J1" s="28"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B2" s="29" t="s">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="B2" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
       <c r="H2" s="3"/>
       <c r="I2" s="19" t="s">
         <v>27</v>
@@ -954,7 +957,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
       <c r="H3" s="17" t="s">
         <v>17</v>
       </c>
@@ -965,14 +968,14 @@
         <v>237</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
       <c r="C4" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="30" t="s">
+      <c r="D4" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="30"/>
+      <c r="E4" s="33"/>
       <c r="H4" s="17" t="s">
         <v>18</v>
       </c>
@@ -983,14 +986,14 @@
         <v>237</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
       <c r="C5" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="31" t="s">
+      <c r="D5" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="E5" s="32"/>
+      <c r="E5" s="35"/>
       <c r="H5" s="17" t="s">
         <v>19</v>
       </c>
@@ -1001,7 +1004,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
       <c r="B6" s="8"/>
       <c r="C6" s="9" t="s">
         <v>2</v>
@@ -1011,7 +1014,7 @@
       </c>
       <c r="E6" s="27"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
       <c r="C7" s="9" t="s">
         <v>1</v>
       </c>
@@ -1020,7 +1023,7 @@
       </c>
       <c r="E7" s="27"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.45">
       <c r="B9" s="10" t="s">
         <v>4</v>
       </c>
@@ -1034,7 +1037,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="165" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" ht="142.5" x14ac:dyDescent="0.45">
       <c r="B10" s="23">
         <v>1</v>
       </c>
@@ -1048,7 +1051,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="135" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" ht="128.25" x14ac:dyDescent="0.45">
       <c r="B11" s="23">
         <f>B10+1</f>
         <v>2</v>
@@ -1063,7 +1066,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="150" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" ht="114" x14ac:dyDescent="0.45">
       <c r="B12" s="23">
         <f t="shared" ref="B12:B25" si="0">B11+1</f>
         <v>3</v>
@@ -1078,7 +1081,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.45">
       <c r="B13" s="3">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -1087,7 +1090,7 @@
       <c r="D13" s="1"/>
       <c r="E13" s="2"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.45">
       <c r="B14" s="3">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -1096,7 +1099,7 @@
       <c r="D14" s="1"/>
       <c r="E14" s="2"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.45">
       <c r="B15" s="3">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -1105,7 +1108,7 @@
       <c r="D15" s="1"/>
       <c r="E15" s="2"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.45">
       <c r="B16" s="3">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -1114,7 +1117,7 @@
       <c r="D16" s="1"/>
       <c r="E16" s="2"/>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B17" s="3">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -1123,7 +1126,7 @@
       <c r="D17" s="1"/>
       <c r="E17" s="2"/>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B18" s="3">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -1132,7 +1135,7 @@
       <c r="D18" s="3"/>
       <c r="E18" s="15"/>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B19" s="3">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -1141,7 +1144,7 @@
       <c r="D19" s="3"/>
       <c r="E19" s="15"/>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B20" s="3">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -1150,7 +1153,7 @@
       <c r="D20" s="3"/>
       <c r="E20" s="15"/>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B21" s="3">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -1159,7 +1162,7 @@
       <c r="D21" s="3"/>
       <c r="E21" s="15"/>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B22" s="3">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -1168,7 +1171,7 @@
       <c r="D22" s="3"/>
       <c r="E22" s="15"/>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B23" s="3">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -1177,7 +1180,7 @@
       <c r="D23" s="3"/>
       <c r="E23" s="15"/>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B24" s="3">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -1186,7 +1189,7 @@
       <c r="D24" s="3"/>
       <c r="E24" s="15"/>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B25" s="3">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -1195,7 +1198,7 @@
       <c r="D25" s="3"/>
       <c r="E25" s="15"/>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:5" x14ac:dyDescent="0.45">
       <c r="C27" s="11" t="s">
         <v>8</v>
       </c>
@@ -1224,18 +1227,18 @@
     <tabColor theme="9" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="A1:J28"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="9" style="6"/>
-    <col min="2" max="2" width="12.28515625" style="6" customWidth="1"/>
-    <col min="3" max="4" width="16.28515625" style="6" customWidth="1"/>
-    <col min="5" max="5" width="41.42578125" style="6" customWidth="1"/>
+    <col min="2" max="2" width="12.265625" style="6" customWidth="1"/>
+    <col min="3" max="4" width="16.265625" style="6" customWidth="1"/>
+    <col min="5" max="5" width="41.3984375" style="6" customWidth="1"/>
     <col min="6" max="8" width="9" style="6"/>
     <col min="9" max="9" width="22" style="6" customWidth="1"/>
     <col min="10" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A1" s="4"/>
       <c r="B1" s="5" t="s">
         <v>3</v>
@@ -1246,13 +1249,13 @@
       <c r="I1" s="28"/>
       <c r="J1" s="28"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B2" s="29" t="s">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="B2" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
       <c r="H2" s="3"/>
       <c r="I2" s="19" t="s">
         <v>27</v>
@@ -1261,7 +1264,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
       <c r="H3" s="17" t="s">
         <v>17</v>
       </c>
@@ -1272,14 +1275,14 @@
         <v>237</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
       <c r="C4" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="33" t="s">
+      <c r="D4" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="33"/>
+      <c r="E4" s="36"/>
       <c r="H4" s="17" t="s">
         <v>18</v>
       </c>
@@ -1290,14 +1293,14 @@
         <v>237</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
       <c r="C5" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="34" t="s">
+      <c r="D5" s="37" t="s">
         <v>30</v>
       </c>
-      <c r="E5" s="35"/>
+      <c r="E5" s="38"/>
       <c r="H5" s="17" t="s">
         <v>19</v>
       </c>
@@ -1308,7 +1311,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
       <c r="B6" s="8"/>
       <c r="C6" s="9" t="s">
         <v>2</v>
@@ -1318,7 +1321,7 @@
       </c>
       <c r="E6" s="27"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
       <c r="C7" s="9" t="s">
         <v>1</v>
       </c>
@@ -1327,7 +1330,7 @@
       </c>
       <c r="E7" s="27"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.45">
       <c r="B9" s="10" t="s">
         <v>4</v>
       </c>
@@ -1341,7 +1344,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="135" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" ht="128.25" x14ac:dyDescent="0.45">
       <c r="B10" s="23">
         <v>1</v>
       </c>
@@ -1355,7 +1358,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="180" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" ht="142.5" x14ac:dyDescent="0.45">
       <c r="B11" s="23">
         <f>B10+1</f>
         <v>2</v>
@@ -1370,7 +1373,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="150" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" ht="114" x14ac:dyDescent="0.45">
       <c r="B12" s="23">
         <f t="shared" ref="B12:B26" si="0">B11+1</f>
         <v>3</v>
@@ -1385,7 +1388,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.45">
       <c r="B13" s="3">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -1394,7 +1397,7 @@
       <c r="D13" s="1"/>
       <c r="E13" s="2"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.45">
       <c r="B14" s="3">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -1403,7 +1406,7 @@
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.45">
       <c r="B15" s="3">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -1412,7 +1415,7 @@
       <c r="D15" s="1"/>
       <c r="E15" s="2"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.45">
       <c r="B16" s="3">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -1421,7 +1424,7 @@
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B17" s="3">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -1430,7 +1433,7 @@
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B18" s="3">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -1439,7 +1442,7 @@
       <c r="D18" s="1"/>
       <c r="E18" s="2"/>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B19" s="3">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -1448,7 +1451,7 @@
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B20" s="3">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -1457,7 +1460,7 @@
       <c r="D20" s="1"/>
       <c r="E20" s="2"/>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B21" s="3">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -1466,7 +1469,7 @@
       <c r="D21" s="1"/>
       <c r="E21" s="2"/>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B22" s="3">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -1475,7 +1478,7 @@
       <c r="D22" s="1"/>
       <c r="E22" s="2"/>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B23" s="3">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -1484,7 +1487,7 @@
       <c r="D23" s="1"/>
       <c r="E23" s="2"/>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B24" s="3">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -1493,7 +1496,7 @@
       <c r="D24" s="1"/>
       <c r="E24" s="2"/>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B25" s="3">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -1502,7 +1505,7 @@
       <c r="D25" s="1"/>
       <c r="E25" s="2"/>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B26" s="3">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -1511,7 +1514,7 @@
       <c r="D26" s="1"/>
       <c r="E26" s="2"/>
     </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:5" x14ac:dyDescent="0.45">
       <c r="C28" s="11" t="s">
         <v>8</v>
       </c>
@@ -1540,19 +1543,19 @@
     <tabColor theme="3" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="A1:J32"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="9" style="6"/>
-    <col min="2" max="2" width="12.28515625" style="6" customWidth="1"/>
-    <col min="3" max="3" width="16.28515625" style="6" customWidth="1"/>
+    <col min="2" max="2" width="12.265625" style="6" customWidth="1"/>
+    <col min="3" max="3" width="16.265625" style="6" customWidth="1"/>
     <col min="4" max="4" width="18" style="6" customWidth="1"/>
-    <col min="5" max="5" width="41.42578125" style="6" customWidth="1"/>
+    <col min="5" max="5" width="41.3984375" style="6" customWidth="1"/>
     <col min="6" max="8" width="9" style="6"/>
-    <col min="9" max="9" width="26.7109375" style="6" customWidth="1"/>
+    <col min="9" max="9" width="26.73046875" style="6" customWidth="1"/>
     <col min="10" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A1" s="4"/>
       <c r="B1" s="5" t="s">
         <v>3</v>
@@ -1563,13 +1566,13 @@
       <c r="I1" s="28"/>
       <c r="J1" s="28"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B2" s="29" t="s">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="B2" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
       <c r="H2" s="3"/>
       <c r="I2" s="19" t="s">
         <v>27</v>
@@ -1578,7 +1581,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
       <c r="H3" s="17" t="s">
         <v>17</v>
       </c>
@@ -1589,14 +1592,14 @@
         <v>237</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
       <c r="C4" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="36" t="s">
+      <c r="D4" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="36"/>
+      <c r="E4" s="29"/>
       <c r="H4" s="17" t="s">
         <v>18</v>
       </c>
@@ -1607,14 +1610,14 @@
         <v>237</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
       <c r="C5" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="37" t="s">
+      <c r="D5" s="31" t="s">
         <v>30</v>
       </c>
-      <c r="E5" s="38"/>
+      <c r="E5" s="32"/>
       <c r="H5" s="17" t="s">
         <v>19</v>
       </c>
@@ -1625,7 +1628,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
       <c r="B6" s="8"/>
       <c r="C6" s="9" t="s">
         <v>2</v>
@@ -1635,7 +1638,7 @@
       </c>
       <c r="E6" s="27"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
       <c r="C7" s="9" t="s">
         <v>1</v>
       </c>
@@ -1644,7 +1647,7 @@
       </c>
       <c r="E7" s="27"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.45">
       <c r="B9" s="10" t="s">
         <v>4</v>
       </c>
@@ -1658,7 +1661,10 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="195" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" ht="171" x14ac:dyDescent="0.45">
+      <c r="A10" s="21" t="s">
+        <v>81</v>
+      </c>
       <c r="B10" s="24">
         <v>1</v>
       </c>
@@ -1672,7 +1678,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="195" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" ht="171" x14ac:dyDescent="0.45">
       <c r="B11" s="24">
         <f>B10+1</f>
         <v>2</v>
@@ -1687,7 +1693,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="180" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" ht="156.75" x14ac:dyDescent="0.45">
       <c r="B12" s="24">
         <f t="shared" ref="B12:B30" si="0">B11+1</f>
         <v>3</v>
@@ -1702,7 +1708,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.45">
       <c r="B13" s="3">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -1711,7 +1717,7 @@
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.45">
       <c r="B14" s="3">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -1720,7 +1726,7 @@
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.45">
       <c r="B15" s="3">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -1729,7 +1735,7 @@
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.45">
       <c r="B16" s="3">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -1738,7 +1744,7 @@
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B17" s="3">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -1747,7 +1753,7 @@
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B18" s="3">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -1756,7 +1762,7 @@
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B19" s="3">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -1765,7 +1771,7 @@
       <c r="D19" s="1"/>
       <c r="E19" s="2"/>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B20" s="3">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -1774,7 +1780,7 @@
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B21" s="3">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -1783,7 +1789,7 @@
       <c r="D21" s="1"/>
       <c r="E21" s="2"/>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B22" s="3">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -1792,7 +1798,7 @@
       <c r="D22" s="2"/>
       <c r="E22" s="2"/>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B23" s="3">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -1801,7 +1807,7 @@
       <c r="D23" s="2"/>
       <c r="E23" s="2"/>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B24" s="3">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -1810,7 +1816,7 @@
       <c r="D24" s="2"/>
       <c r="E24" s="2"/>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B25" s="3">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -1819,7 +1825,7 @@
       <c r="D25" s="2"/>
       <c r="E25" s="2"/>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B26" s="3">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -1828,7 +1834,7 @@
       <c r="D26" s="1"/>
       <c r="E26" s="2"/>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B27" s="3">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -1837,7 +1843,7 @@
       <c r="D27" s="2"/>
       <c r="E27" s="1"/>
     </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B28" s="3">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -1846,7 +1852,7 @@
       <c r="D28" s="2"/>
       <c r="E28" s="2"/>
     </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B29" s="3">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -1855,7 +1861,7 @@
       <c r="D29" s="2"/>
       <c r="E29" s="2"/>
     </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B30" s="3">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -1864,7 +1870,7 @@
       <c r="D30" s="2"/>
       <c r="E30" s="2"/>
     </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:5" x14ac:dyDescent="0.45">
       <c r="C32" s="11" t="s">
         <v>8</v>
       </c>
@@ -1893,20 +1899,20 @@
     <tabColor theme="6" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:J35"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="9" style="6"/>
-    <col min="2" max="2" width="12.28515625" style="6" customWidth="1"/>
-    <col min="3" max="3" width="16.28515625" style="6" customWidth="1"/>
+    <col min="2" max="2" width="12.265625" style="6" customWidth="1"/>
+    <col min="3" max="3" width="16.265625" style="6" customWidth="1"/>
     <col min="4" max="4" width="18" style="6" customWidth="1"/>
     <col min="5" max="5" width="24" style="6" customWidth="1"/>
-    <col min="6" max="6" width="16.5703125" style="6" customWidth="1"/>
+    <col min="6" max="6" width="16.59765625" style="6" customWidth="1"/>
     <col min="7" max="8" width="9" style="6"/>
-    <col min="9" max="9" width="26.7109375" style="6" customWidth="1"/>
+    <col min="9" max="9" width="26.73046875" style="6" customWidth="1"/>
     <col min="10" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A1" s="4"/>
       <c r="B1" s="5" t="s">
         <v>3</v>
@@ -1917,13 +1923,13 @@
       <c r="I1" s="28"/>
       <c r="J1" s="28"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B2" s="29" t="s">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="B2" s="30" t="s">
         <v>28</v>
       </c>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
       <c r="H2" s="3"/>
       <c r="I2" s="19" t="s">
         <v>27</v>
@@ -1932,7 +1938,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
       <c r="H3" s="17" t="s">
         <v>17</v>
       </c>
@@ -1943,12 +1949,12 @@
         <v>237</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
       <c r="C4" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="36"/>
-      <c r="E4" s="36"/>
+      <c r="D4" s="29"/>
+      <c r="E4" s="29"/>
       <c r="H4" s="17" t="s">
         <v>18</v>
       </c>
@@ -1959,7 +1965,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
       <c r="C5" s="9" t="s">
         <v>2</v>
       </c>
@@ -1977,7 +1983,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
       <c r="B6" s="8"/>
       <c r="C6" s="9" t="s">
         <v>1</v>
@@ -1988,7 +1994,7 @@
       <c r="E6" s="27"/>
       <c r="F6" s="20"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.45">
       <c r="B9" s="10" t="s">
         <v>4</v>
       </c>
@@ -2005,7 +2011,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" ht="57" x14ac:dyDescent="0.45">
       <c r="B10" s="24">
         <v>1</v>
       </c>
@@ -2022,7 +2028,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" ht="42.75" x14ac:dyDescent="0.45">
       <c r="B11" s="24">
         <f>B10+1</f>
         <v>2</v>
@@ -2040,7 +2046,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" ht="42.75" x14ac:dyDescent="0.45">
       <c r="B12" s="24">
         <f t="shared" ref="B12:B30" si="0">B11+1</f>
         <v>3</v>
@@ -2058,7 +2064,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" ht="57" x14ac:dyDescent="0.45">
       <c r="B13" s="24">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -2076,7 +2082,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" ht="42.75" x14ac:dyDescent="0.45">
       <c r="B14" s="24">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -2094,7 +2100,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.45">
       <c r="B15" s="3">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -2104,7 +2110,7 @@
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.45">
       <c r="B16" s="3">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -2114,7 +2120,7 @@
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B17" s="3">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -2124,7 +2130,7 @@
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B18" s="3">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -2134,7 +2140,7 @@
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B19" s="3">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -2144,7 +2150,7 @@
       <c r="E19" s="2"/>
       <c r="F19" s="2"/>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B20" s="3">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -2154,7 +2160,7 @@
       <c r="E20" s="2"/>
       <c r="F20" s="2"/>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B21" s="3">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -2164,7 +2170,7 @@
       <c r="E21" s="2"/>
       <c r="F21" s="2"/>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B22" s="3">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -2174,7 +2180,7 @@
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B23" s="3">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -2184,7 +2190,7 @@
       <c r="E23" s="2"/>
       <c r="F23" s="2"/>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B24" s="3">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -2194,7 +2200,7 @@
       <c r="E24" s="2"/>
       <c r="F24" s="2"/>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B25" s="3">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -2204,7 +2210,7 @@
       <c r="E25" s="2"/>
       <c r="F25" s="2"/>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B26" s="3">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -2214,7 +2220,7 @@
       <c r="E26" s="2"/>
       <c r="F26" s="2"/>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B27" s="3">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -2224,7 +2230,7 @@
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B28" s="3">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -2234,7 +2240,7 @@
       <c r="E28" s="2"/>
       <c r="F28" s="2"/>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B29" s="3">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -2244,7 +2250,7 @@
       <c r="E29" s="2"/>
       <c r="F29" s="2"/>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B30" s="3">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -2254,7 +2260,7 @@
       <c r="E30" s="2"/>
       <c r="F30" s="2"/>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:6" x14ac:dyDescent="0.45">
       <c r="C32" s="39" t="s">
         <v>29</v>
       </c>
@@ -2264,7 +2270,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="35" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="6:6" x14ac:dyDescent="0.45">
       <c r="F35" s="21"/>
     </row>
   </sheetData>
